--- a/packages/rc9_2_2_production/inputs/NMG_EN_FIXED_NESTING_REST_SAFE_REGRESSION_CLEAN.xlsx
+++ b/packages/rc9_2_2_production/inputs/NMG_EN_FIXED_NESTING_REST_SAFE_REGRESSION_CLEAN.xlsx
@@ -1,40 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Engine Defaults" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RC9 Universal Setup" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RC9.1 Release Notes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="00 START HERE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FT Wise 15 Min" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FT Wise 30 Min" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="FT Wise 60 Min" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Shrinkage 15 Min" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Shrinkage 30 Min" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Shrinkage 60 Min" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Shift Library" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Language Setup" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Preference" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Fixed Request" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Previous week scheduled" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Shift Catalog" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Validation Lists" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Input Checks" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC9 Universal Setup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC9.1 Release Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 START HERE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engine Defaults" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 15 Min" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 30 Min" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 60 Min" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 15 Min" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 30 Min" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 60 Min" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Library" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Language Setup" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Request" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previous week scheduled" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Checks" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Catalog" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Lists" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engine Defaults'!$A$1:$D$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Shift Library'!$A$1:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Language Setup'!$A$1:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Shift Catalog'!$A$1:$D$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Validation Lists'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Input Checks'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Shift Catalog'!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Validation Lists'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -45,7 +47,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,24 +81,8 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -133,23 +119,8 @@
         <fgColor rgb="FFE4DFEC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -181,25 +152,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -259,14 +216,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1004,646 +953,287 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="20" min="1" max="1"/>
-    <col width="48" customWidth="1" style="20" min="2" max="2"/>
-    <col width="30" customWidth="1" style="20" min="3" max="3"/>
-    <col width="62" customWidth="1" style="20" min="4" max="4"/>
+    <col width="42" customWidth="1" style="20" min="1" max="1"/>
+    <col width="105" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15" customWidth="1" style="20" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>SETUP - the decisions you make for this schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="20">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Fill the Value column. Cells with a dropdown accept only the listed options. Anything left blank uses the engine default and is marked in Notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>RC9.1 Universal Search-Recovery Production Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>Notes</t>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="20">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>This workbook is the only input contract for the RC9.1 universal engine. It is prepared for a full 24/7 GDI REAL28 weekly case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Production rule</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Program/client name is metadata only; solver behavior is controlled by Instructions, Shift Library, Language Setup, requests, and requirement sheets.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Program Name</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>NMG_EN</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Primary KPI</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Target is dynamic; this case explicitly targets 100% per interval with 80% protected floor.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr"/>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>Count of Associates</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="D6" s="27" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Required output 1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BEST_BEFORE_BREAKS_SCHEDULE is the review/anchor artifact only.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Allow Headcount Mismatch</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Required output 2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>BEST_FINAL_AFTER_BREAKS_SCHEDULE is the operational after-break artifact.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr"/>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Interval Minutes</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" s="27" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Search Recovery</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>RC9.1 should expand break search across target Pareto skeletons rather than exhaust a single skeleton.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr"/>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>Requirements Source</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>FT Wise 30 Min</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Deep Mode</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Default Deep runtime up to 4 hours.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr"/>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Shrinkage Source</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
-        <is>
-          <t>Shrinkage 30 Min</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>How To Run</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Run Stage</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>Full Schedule</t>
-        </is>
-      </c>
-      <c r="D12" s="27" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Full Mode</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Default Full runtime up to 6 hours for tight 24/7 cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Universal Scope</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>No client-specific production branch is implied by Program Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="20">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>24/7 Input Contract</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24x7 operating week; blank demand intervals are intentional and governed by Blank Interval Staffing Rule. Do not force blanks to zero.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr"/>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Run Depth</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>Deep</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="n"/>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Workbook completion checklist</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D15" s="27" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr"/>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Target Priority Confirmed</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Instructions values completed</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="20">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Schedule roster rows completed, one associate per row</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr"/>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Minimum Per Interval</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D17" s="27" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr"/>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Hard Floor Solver Constraint Enabled</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Requirement sheet selected and populated</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="20">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Matching shrinkage sheet selected and populated</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr"/>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Blank Interval Staffing Rule</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>No new staffing in blank intervals</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Shift Library contains only allowed 9H shifts</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Language Setup completed</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Allowed Shift Durations Hours</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D21" s="27" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Request completed/disabled</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr"/>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Use 11H/3OFF</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D22" s="27" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Previous week scheduled completed</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr"/>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Strict OFF Count</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr"/>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>Separate OFF Days</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr"/>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Rest Gap Hours</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" s="27" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr"/>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>Count of Different Shifts Per week</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="27" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>Fixed Request Use</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr"/>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Hard OFF Preferences</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr"/>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>Leave Enabled</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr"/>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>Use Preferences</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D31" s="27" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Opening Guard</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>Opening Guard Enabled</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr"/>
-      <c r="B34" s="27" t="inlineStr">
-        <is>
-          <t>Opening Minimum FTE</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="27" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr"/>
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>Opening Guard Intervals</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="27" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>Short Break Count</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="27" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="27" t="inlineStr"/>
-      <c r="B38" s="27" t="inlineStr">
-        <is>
-          <t>Short Break Duration Minutes</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D38" s="27" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="27" t="inlineStr"/>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>Lunch Count</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="27" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="27" t="inlineStr"/>
-      <c r="B40" s="27" t="inlineStr">
-        <is>
-          <t>Lunch Duration Minutes</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="D40" s="27" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="27" t="inlineStr"/>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>Break Preferred Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="n">
-        <v>150</v>
-      </c>
-      <c r="D41" s="27" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="27" t="inlineStr"/>
-      <c r="B42" s="27" t="inlineStr">
-        <is>
-          <t>Break Absolute Minimum Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="n">
-        <v>60</v>
-      </c>
-      <c r="D42" s="27" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr"/>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>Break Normal Maximum Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="n">
-        <v>210</v>
-      </c>
-      <c r="D43" s="27" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="27" t="inlineStr"/>
-      <c r="B44" s="27" t="inlineStr">
-        <is>
-          <t>Allow Back-to-Back Breaks</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D44" s="27" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
-        <is>
-          <t>Exception Policy</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>Critical Coverage No-Break Exception Enabled</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D46" s="27" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr"/>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>Critical Coverage No-Break Max Associate-Days</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="27" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="26" t="inlineStr">
-        <is>
-          <t>Release Quality</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>Production Quality Gate Mode</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D49" s="27" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="27" t="inlineStr"/>
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>Minimum After Break Target Ratio</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr"/>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>not set - engine default applies</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr"/>
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>Protected Before80 Minimum Intervals</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr"/>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>not set - engine default applies</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr"/>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>Protected After80 Minimum Intervals</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="inlineStr"/>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>not set - engine default applies</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Input Checks reviewed before upload</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <autoFilter ref="A1:C23"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <dataValidations count="7">
-    <dataValidation sqref="C7 C16 C18 C22 C23 C24 C28 C29 C30 C31 C33 C44 C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"15,30,60"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FT Wise 15 Min,FT Wise 30 Min,FT Wise 60 Min"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Shrinkage 15 Min,Shrinkage 30 Min,Shrinkage 60 Min"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Before Breaks Only,Full Schedule"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Quick,Deep,Overnight"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Warn,Fail,Off"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7790,6 +7380,482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" style="20" min="1" max="1"/>
+    <col width="12" customWidth="1" style="20" min="2" max="2"/>
+    <col width="55" customWidth="1" style="20" min="3" max="3"/>
+    <col width="48" customWidth="1" style="20" min="4" max="4"/>
+    <col width="34" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Input Checks — RC9.1 readiness gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>What is tested</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Action when not OK</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Result detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="20">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Interval and requirement source align</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Interval Minutes matches selected FT Wise source.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Choose matching source in Instructions.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>FT Wise 30 Min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Interval and shrinkage source align</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Interval Minutes matches selected shrinkage source.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Choose matching shrinkage source.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Shrinkage 30 Min / 30 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Roster has associates</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Named roster rows are present.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Complete Schedule roster.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42 named associates</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Roster languages complete</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Every named row has a language.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Complete language cells.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0 missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Roster names are unique</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>No duplicate SF Names.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Correct duplicates.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42 unique names</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" s="20">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Requirements pattern loaded</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Selected requirement grid contains the supplied 24x7 hourly pattern, including intentional blank demand intervals.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Review FT Wise 60 Min if any blanks are unintended.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>252 numeric 30-minute demand cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="20">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Blank demand handling aligned</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Blank demand cells are allowed by the explicit Blank Interval Staffing Rule.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Change only if business requires staffing in those intervals.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Intentional blanks preserved; no forced zero-fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="20">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Shrinkage pattern loaded</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Matching shrinkage source preserves the supplied pattern; blanks are retained rather than converted.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Review Shrinkage 60 Min only if the source business rule changes.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>182 numeric shrinkage cells; intentional blanks preserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Allowed shifts loaded</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>24 hourly 9H shifts are allowed.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Review Shift Library.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24 allowed 9H shifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11H settings align</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11H is disabled and only 9H is allowed.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Align shift pattern settings.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9H only / 11H=No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="20">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Fixed requests ready</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Request Use is enabled and active rows are present.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Review exact shift/OFF rows if business changes them.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30 active fixed/nesting rows; 12 associates remain flexible</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Break exception policy explicit</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No-break exception policy is explicit and capped.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Change only with explicit business approval.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Enabled / cap 7 associate-days</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="20">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Cyclic carry-in loaded</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Previous Saturday is populated for 26 of 32 named associates.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Populate missing history if those associates need prior-week Sunday carry-in protection.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12 supplied; remaining associates have no prior-Saturday row and are treated per contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="20">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Language direction aligned</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Bilingual self-coverage is explicitly included; UK and French retain source-language coverage.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Correct Can Cover Languages if business logic changes.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Directional coverage aligned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Overall readiness</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Core RC9.1 contract is internally consistent, but cyclic prior-Saturday history is incomplete for 6 associates.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Populate/confirm the missing 6 before a production-grade cyclic run.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RUN-READY WITH CYCLIC HISTORY WARNING</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E16"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B3:B16">
+    <cfRule type="expression" priority="1" dxfId="13">
+      <formula>B3="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="12">
+      <formula>OR(B3="CHECK",B3="REVIEW")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="11">
+      <formula>B3="MISSING"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8797,7 +8863,229 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="50" customWidth="1" style="20" min="3" max="3"/>
+    <col width="12" customWidth="1" style="20" min="4" max="4"/>
+    <col width="42" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>RC9.1 Release Notes — Input-specific choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>This workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Target handling</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Workbook Target is primary</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Prevents floor-first misoptimization</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Target=100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2 breaks</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Breadth-first across Pareto skeletons</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Improves recovery on tight 24/7 cases</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Keep default</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Joint recovery</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Deep 4h / Full 6h</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tight 24/7 needs integrated recovery time</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Keep default</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="20">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Break spacing</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>120 preferred, 60 absolute minimum</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Prevents false break infeasibility on overnight-heavy 24/7 schedules</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60-min absolute minimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Blank demand</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No new staffing in blank intervals</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Avoids invented demand</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No blank intervals exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Directional source -&gt; cover list</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Prevents over-expanding UK/Bilingual eligibility</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UK + English; Bilingual + French + English</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9027,951 +9315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="20" min="1" max="1"/>
-    <col width="48" customWidth="1" style="20" min="2" max="2"/>
-    <col width="30" customWidth="1" style="20" min="3" max="3"/>
-    <col width="62" customWidth="1" style="20" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>ADVANCED - engine tuning. Defaults are production-tested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="20">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Change these only with a specific reason. They are not per-schedule business settings; the values here are the ones every released result was measured with.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>Demand Fit</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Demand Fit Guard Enabled</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr"/>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>Demand Fit Minimum Active Minutes</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>180</v>
-      </c>
-      <c r="D6" s="27" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Demand Fit Minimum Active Ratio</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D7" s="27" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr"/>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Demand Fit Maximum Blank Span Minutes</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>180</v>
-      </c>
-      <c r="D8" s="27" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Overage Control</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Overage Control Enabled</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr"/>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Overage Soft Cap</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D11" s="27" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr"/>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Overage Severe Cap</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D12" s="27" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr"/>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Overage Extreme Cap</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D13" s="27" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr"/>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>Overage Penalty Weight</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="D14" s="27" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>Break Concurrency</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Maximum Concurrent Break Ratio</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D16" s="27" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr"/>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Maximum Concurrent Breaks</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="27" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr"/>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Break Concurrency Gate Mode</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Week Boundary</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>Next Sunday Balance Enabled</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr"/>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Next Sunday Overage Cap</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D21" s="27" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr"/>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Next Sunday Maximum Adjacent Raw Change</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="27" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr"/>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Next Sunday Balance Gate Mode</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Language / Skill</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Language Operational Reserve Enabled</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr"/>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>Language Operational Reserve Extra FTE</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="27" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr"/>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>Language Reserve Gate Mode</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr"/>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>Qualified Language Break Certificate Enabled</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>Whole Week Balance</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>Whole Week Balance Enabled</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr"/>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>Whole Week Overage Cap</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D31" s="27" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>Quality Benchmark Tolerance Intervals</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="27" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Auto,Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C10 C20 C25 C28 C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C18 C23 C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Warn,Fail,Off"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>Input Checks are performed by the engine, not by this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1" s="20">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>The previous version of this tab held hardcoded PASS/WARN text. It reported PASS regardless of what the roster, demand or language setup actually contained, so it could not catch the errors it appeared to check for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>The engine runs the real pre-solver contract validation on every run and writes the result to the audit JSON as pre_solver_contract_validation, with a specific code, day and time for each failure. That is the authoritative check.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" style="20" min="1" max="1"/>
-    <col width="105" customWidth="1" style="20" min="2" max="2"/>
-    <col width="15" customWidth="1" style="20" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>RC9.1 Universal Search-Recovery Production Setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="20">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>This workbook is the only input contract for the RC9.1 universal engine. It is prepared for a full 24/7 GDI REAL28 weekly case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Production rule</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Program/client name is metadata only; solver behavior is controlled by Instructions, Shift Library, Language Setup, requests, and requirement sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Primary KPI</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Target is dynamic; this case explicitly targets 100% per interval with 80% protected floor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Required output 1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BEST_BEFORE_BREAKS_SCHEDULE is the review/anchor artifact only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Required output 2</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>BEST_FINAL_AFTER_BREAKS_SCHEDULE is the operational after-break artifact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Search Recovery</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>RC9.1 should expand break search across target Pareto skeletons rather than exhaust a single skeleton.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Deep Mode</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Default Deep runtime up to 4 hours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Full Mode</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Default Full runtime up to 6 hours for tight 24/7 cases.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Universal Scope</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>No client-specific production branch is implied by Program Name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="20">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>24/7 Input Contract</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>24x7 operating week; blank demand intervals are intentional and governed by Blank Interval Staffing Rule. Do not force blanks to zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Workbook completion checklist</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Instructions values completed</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="20">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Schedule roster rows completed, one associate per row</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Requirement sheet selected and populated</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="20">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Matching shrinkage sheet selected and populated</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Shift Library contains only allowed 9H shifts</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Language Setup completed</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Request completed/disabled</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Previous week scheduled completed</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Input Checks reviewed before upload</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C23"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="20" min="1" max="1"/>
-    <col width="34" customWidth="1" style="20" min="2" max="2"/>
-    <col width="50" customWidth="1" style="20" min="3" max="3"/>
-    <col width="12" customWidth="1" style="20" min="4" max="4"/>
-    <col width="42" customWidth="1" style="20" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>RC9.1 Release Notes — Input-specific choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>This workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Target handling</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Workbook Target is primary</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Prevents floor-first misoptimization</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Target=100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Stage 2 breaks</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Breadth-first across Pareto skeletons</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Improves recovery on tight 24/7 cases</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Keep default</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Joint recovery</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Deep 4h / Full 6h</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Tight 24/7 needs integrated recovery time</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Keep default</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="20">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Break spacing</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>120 preferred, 60 absolute minimum</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Prevents false break infeasibility on overnight-heavy 24/7 schedules</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60-min absolute minimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Blank demand</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>No new staffing in blank intervals</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Avoids invented demand</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>No blank intervals exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Directional source -&gt; cover list</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Prevents over-expanding UK/Bilingual eligibility</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>UK + English; Bilingual + French + English</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E8"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10127,6 +9471,1345 @@
   <autoFilter ref="A1:G8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="40" customWidth="1" style="20" min="2" max="2"/>
+    <col width="34" customWidth="1" style="20" min="3" max="3"/>
+    <col width="65" customWidth="1" style="20" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Instructions — RC9.1 Universal Business Contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>What this controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>NMG_EN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Metadata only; no solver branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Interval Minutes</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Matches FT Wise 30 Min / Shrinkage 30 Min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Requirements Source</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>FT Wise 30 Min</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Selected demand grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Shrinkage Source</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Shrinkage 30 Min</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Matching shrinkage grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Primary after-break target tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Target Priority Confirmed</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Confirms this 90% target is intentional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Minimum Per Interval</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Protected floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hard Floor Solver Constraint Enabled</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Floor protected; target remains primary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Blank Interval Staffing Rule</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>No new staffing in blank intervals</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No current-week staffing in blank demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Allowed Shift Durations Hours</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Only 9H shifts are allowed in this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Use 11H/3OFF</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly disabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Strict OFF Count</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2 OFF for 9H/2OFF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="20">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Separate OFF Days</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Normal consecutive OFF preference; explicit preference OFF still honored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Rest Gap Hours</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Minimum rest gap, including week boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Count of Different Shifts Per week</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Maximum distinct shifts in week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Request Use</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Active exact fixed shift/OFF rows in Fixed Request are honored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Hard OFF Preferences</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>OFF in Preference is hard when present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Leave Enabled</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Leave is hard unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Use Preferences</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Soft shift/OFF preferences are used where not hard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Opening Guard</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Opening Guard Enabled</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Not imposed by this input unless business contract is changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Opening Guard</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Opening Minimum FTE</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Control value if enabled later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Opening Guard</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Opening Guard Intervals</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Control value if enabled later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Short Break Count</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Two 15-minute short breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Short Break Duration Minutes</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Per short break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Lunch Count</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>One lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Lunch Duration Minutes</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Lunch duration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Break Preferred Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Preferred spacing, not the hard minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Break Absolute Minimum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hard minimum spacing between break segments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Break Normal Maximum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Normal spacing target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Allow Back-to-Back Breaks</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>No compressed back-to-back breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" s="20">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Exception Policy</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Critical Coverage No-Break Exception Enabled</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Do not silently allow no-break exceptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" s="20">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Exception Policy</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Critical Coverage No-Break Max Associate-Days</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>No operational no-break exceptions approved in input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Release Quality</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Production Quality Gate Mode</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Hard-valid schedule can be reviewed if quality debt appears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Count of Associates</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Must match named roster rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Allow Headcount Mismatch</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Do not silently accept mismatch.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="10">
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Enable 11H only when explicitly approved." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Strict OFF count control." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Use fixed/nesting only with real requests." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Hard OFF preference control." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Leave control." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Use soft preferences." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Opening guard." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Back-to-back break override." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="No-break exception permission." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Release gate mode." type="list">
+      <formula1>"Fail,Warn,Off"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="54" customWidth="1" style="20" min="3" max="3"/>
+    <col width="48" customWidth="1" style="20" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Engine Defaults — RC9.1 24/7-safe defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Demand Fit Guard Enabled</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Auto-enable when blank staffing is prohibited.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>24/7 demand has no blank cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Demand Fit Minimum Active Minutes</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Technical demand-fit guard.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Demand Fit Minimum Active Ratio</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Technical demand-fit guard.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Demand Fit Maximum Blank Span Minutes</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Technical guard default.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No blank span in 24/7 input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Overage Control Enabled</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Discourage avoidable overage after coverage protections.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Overage Soft Cap</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic threshold.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Overage Severe Cap</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic threshold.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Overage Extreme Cap</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostic threshold.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Overage Penalty Weight</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Internal objective weight.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Maximum Concurrent Break Ratio</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Operational quality default.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Maximum Concurrent Breaks</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Operational quality default.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Break Concurrency Gate Mode</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Warning unless business changes it.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Next Sunday Balance Enabled</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Protect cyclic carry-out.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Next Sunday Overage Cap</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Cyclic balance default.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Next Sunday Maximum Adjacent Raw Change</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cyclic balance default.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Next Sunday Balance Gate Mode</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Operational warning by default.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Language Operational Reserve Enabled</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Prefer redundancy over only meeting language minimum.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Language Operational Reserve Extra FTE</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Reserve default.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Language Reserve Gate Mode</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Operational warning by default.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Qualified Language Break Certificate Enabled</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Break-feasibility evidence for language coverage.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Whole Week Balance Enabled</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Whole-week balance optimization.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Whole Week Overage Cap</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Balance default.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Quality Benchmark Tolerance Intervals</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Do not let historical benchmark hide current contract.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RC9.1 Deep Default Seconds</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Approx. 4 hours.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RC9.1 Full Default Seconds</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>21600</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Approx. 6 hours.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RC9.1 Stage2 Search Order</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Breadth First</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Expand across Pareto skeletons before exhausting one.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RC9.1 Joint Budget Policy</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Up to 35% of total runtime</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Allow integrated shift/OFF/break recovery.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D29"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0"/>

--- a/packages/rc9_2_2_production/inputs/NMG_EN_FIXED_NESTING_REST_SAFE_REGRESSION_CLEAN.xlsx
+++ b/packages/rc9_2_2_production/inputs/NMG_EN_FIXED_NESTING_REST_SAFE_REGRESSION_CLEAN.xlsx
@@ -1,42 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC9 Universal Setup" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RC9.1 Release Notes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 START HERE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engine Defaults" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 15 Min" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 30 Min" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FT Wise 60 Min" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 15 Min" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 30 Min" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shrinkage 60 Min" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Library" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Language Setup" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preference" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Request" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previous week scheduled" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Checks" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Catalog" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Lists" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Engine Defaults" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RC9 Universal Setup" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RC9.1 Release Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="00 START HERE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Schedule" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FT Wise 15 Min" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FT Wise 30 Min" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FT Wise 60 Min" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Shrinkage 15 Min" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Shrinkage 30 Min" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Shrinkage 60 Min" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Shift Library" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Language Setup" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Preference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Fixed Request" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Previous week scheduled" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Shift Catalog" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Validation Lists" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Input Checks" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Engine Defaults'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RC9 Universal Setup'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RC9.1 Release Notes'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'00 START HERE'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Shift Library'!$A$1:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Language Setup'!$A$1:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Input Checks'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Shift Catalog'!$A$1:$D$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Validation Lists'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Shift Catalog'!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Validation Lists'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -47,7 +45,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +79,24 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -119,8 +133,23 @@
         <fgColor rgb="FFE4DFEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -152,11 +181,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -216,6 +259,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,287 +1004,646 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="20" min="1" max="1"/>
-    <col width="105" customWidth="1" style="20" min="2" max="2"/>
-    <col width="15" customWidth="1" style="20" min="3" max="3"/>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="48" customWidth="1" style="20" min="2" max="2"/>
+    <col width="30" customWidth="1" style="20" min="3" max="3"/>
+    <col width="62" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>RC9.1 Universal Search-Recovery Production Setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>SETUP - the decisions you make for this schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="20">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Fill the Value column. Cells with a dropdown accept only the listed options. Anything left blank uses the engine default and is marked in Notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="20">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>This workbook is the only input contract for the RC9.1 universal engine. It is prepared for a full 24/7 GDI REAL28 weekly case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Production rule</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Program/client name is metadata only; solver behavior is controlled by Instructions, Shift Library, Language Setup, requests, and requirement sheets.</t>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Primary KPI</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Target is dynamic; this case explicitly targets 100% per interval with 80% protected floor.</t>
-        </is>
-      </c>
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Case Setup</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>NMG_EN</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Required output 1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BEST_BEFORE_BREAKS_SCHEDULE is the review/anchor artifact only.</t>
-        </is>
-      </c>
+      <c r="A6" s="27" t="inlineStr"/>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Count of Associates</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>42</v>
+      </c>
+      <c r="D6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Required output 2</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>BEST_FINAL_AFTER_BREAKS_SCHEDULE is the operational after-break artifact.</t>
-        </is>
-      </c>
+      <c r="A7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Allow Headcount Mismatch</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Search Recovery</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>RC9.1 should expand break search across target Pareto skeletons rather than exhaust a single skeleton.</t>
-        </is>
-      </c>
+      <c r="A8" s="27" t="inlineStr"/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Interval Minutes</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="27" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Deep Mode</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Default Deep runtime up to 4 hours.</t>
-        </is>
-      </c>
+      <c r="A9" s="27" t="inlineStr"/>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Requirements Source</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>FT Wise 30 Min</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Full Mode</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Default Full runtime up to 6 hours for tight 24/7 cases.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Universal Scope</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>No client-specific production branch is implied by Program Name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="20">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>24/7 Input Contract</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>24x7 operating week; blank demand intervals are intentional and governed by Blank Interval Staffing Rule. Do not force blanks to zero.</t>
-        </is>
-      </c>
+      <c r="A10" s="27" t="inlineStr"/>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Shrinkage Source</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Shrinkage 30 Min</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>How To Run</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Run Stage</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Full Schedule</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Workbook completion checklist</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="A13" s="27" t="inlineStr"/>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Run Depth</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Deep</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Instructions values completed</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="20">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Schedule roster rows completed, one associate per row</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr"/>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Target Priority Confirmed</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Requirement sheet selected and populated</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="20">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Matching shrinkage sheet selected and populated</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A17" s="27" t="inlineStr"/>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Minimum Per Interval</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr"/>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Hard Floor Solver Constraint Enabled</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Shift Library contains only allowed 9H shifts</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Language Setup completed</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A19" s="27" t="inlineStr"/>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Blank Interval Staffing Rule</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>No new staffing in blank intervals</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Request completed/disabled</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Shift &amp; OFF</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Allowed Shift Durations Hours</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Previous week scheduled completed</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A22" s="27" t="inlineStr"/>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Use 11H/3OFF</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Input Checks reviewed before upload</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="A23" s="27" t="inlineStr"/>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Strict OFF Count</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr"/>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Separate OFF Days</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr"/>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Rest Gap Hours</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr"/>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Count of Different Shifts Per week</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Fixed Request Use</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr"/>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Hard OFF Preferences</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr"/>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Leave Enabled</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr"/>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Use Preferences</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Opening Guard</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Opening Guard Enabled</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr"/>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Opening Minimum FTE</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr"/>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Opening Guard Intervals</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>Breaks</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Short Break Count</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="27" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="inlineStr"/>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Short Break Duration Minutes</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr"/>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Lunch Count</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr"/>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Lunch Duration Minutes</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr"/>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Break Preferred Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="D41" s="27" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr"/>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Break Absolute Minimum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="D42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="27" t="inlineStr"/>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Break Normal Maximum Gap Minutes</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>210</v>
+      </c>
+      <c r="D43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="27" t="inlineStr"/>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>Allow Back-to-Back Breaks</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Exception Policy</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Critical Coverage No-Break Exception Enabled</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr"/>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Critical Coverage No-Break Max Associate-Days</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>Release Quality</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Production Quality Gate Mode</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr"/>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Minimum After Break Target Ratio</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr"/>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>not set - engine default applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr"/>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Protected Before80 Minimum Intervals</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr"/>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>not set - engine default applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr"/>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>Protected After80 Minimum Intervals</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr"/>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>not set - engine default applies</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C23"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <dataValidations count="7">
+    <dataValidation sqref="C7 C16 C18 C22 C23 C24 C28 C29 C30 C31 C33 C44 C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"15,30,60"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"FT Wise 15 Min,FT Wise 30 Min,FT Wise 60 Min"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Shrinkage 15 Min,Shrinkage 30 Min,Shrinkage 60 Min"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Before Breaks Only,Full Schedule"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Quick,Deep,Overnight"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Warn,Fail,Off"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7380,482 +7790,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="31" customWidth="1" style="20" min="1" max="1"/>
-    <col width="12" customWidth="1" style="20" min="2" max="2"/>
-    <col width="55" customWidth="1" style="20" min="3" max="3"/>
-    <col width="48" customWidth="1" style="20" min="4" max="4"/>
-    <col width="34" customWidth="1" style="20" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Input Checks — RC9.1 readiness gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>What is tested</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Action when not OK</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Result detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="20">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Interval and requirement source align</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Interval Minutes matches selected FT Wise source.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Choose matching source in Instructions.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>FT Wise 30 Min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Interval and shrinkage source align</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Interval Minutes matches selected shrinkage source.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Choose matching shrinkage source.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Shrinkage 30 Min / 30 min</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Roster has associates</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Named roster rows are present.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Complete Schedule roster.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42 named associates</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Roster languages complete</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Every named row has a language.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Complete language cells.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0 missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Roster names are unique</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>No duplicate SF Names.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Correct duplicates.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>42 unique names</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1" s="20">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Requirements pattern loaded</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Selected requirement grid contains the supplied 24x7 hourly pattern, including intentional blank demand intervals.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Review FT Wise 60 Min if any blanks are unintended.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>252 numeric 30-minute demand cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="20">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Blank demand handling aligned</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Blank demand cells are allowed by the explicit Blank Interval Staffing Rule.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Change only if business requires staffing in those intervals.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Intentional blanks preserved; no forced zero-fill</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="20">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Shrinkage pattern loaded</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Matching shrinkage source preserves the supplied pattern; blanks are retained rather than converted.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Review Shrinkage 60 Min only if the source business rule changes.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>182 numeric shrinkage cells; intentional blanks preserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Allowed shifts loaded</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>24 hourly 9H shifts are allowed.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Review Shift Library.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24 allowed 9H shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11H settings align</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>11H is disabled and only 9H is allowed.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Align shift pattern settings.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9H only / 11H=No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="20">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Fixed requests ready</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Request Use is enabled and active rows are present.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Review exact shift/OFF rows if business changes them.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30 active fixed/nesting rows; 12 associates remain flexible</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Break exception policy explicit</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>No-break exception policy is explicit and capped.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Change only with explicit business approval.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enabled / cap 7 associate-days</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="20">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic carry-in loaded</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Previous Saturday is populated for 26 of 32 named associates.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Populate missing history if those associates need prior-week Sunday carry-in protection.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12 supplied; remaining associates have no prior-Saturday row and are treated per contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="20">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Language direction aligned</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Bilingual self-coverage is explicitly included; UK and French retain source-language coverage.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Correct Can Cover Languages if business logic changes.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Directional coverage aligned</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Overall readiness</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Core RC9.1 contract is internally consistent, but cyclic prior-Saturday history is incomplete for 6 associates.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Populate/confirm the missing 6 before a production-grade cyclic run.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RUN-READY WITH CYCLIC HISTORY WARNING</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E16"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B3:B16">
-    <cfRule type="expression" priority="1" dxfId="13">
-      <formula>B3="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="12">
-      <formula>OR(B3="CHECK",B3="REVIEW")</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="11">
-      <formula>B3="MISSING"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8863,229 +8797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="20" min="1" max="1"/>
-    <col width="34" customWidth="1" style="20" min="2" max="2"/>
-    <col width="50" customWidth="1" style="20" min="3" max="3"/>
-    <col width="12" customWidth="1" style="20" min="4" max="4"/>
-    <col width="42" customWidth="1" style="20" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>RC9.1 Release Notes — Input-specific choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>This workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Target handling</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Workbook Target is primary</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Prevents floor-first misoptimization</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Target=100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="20">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Stage 2 breaks</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Breadth-first across Pareto skeletons</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Improves recovery on tight 24/7 cases</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Keep default</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Joint recovery</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Deep 4h / Full 6h</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Tight 24/7 needs integrated recovery time</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Keep default</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="20">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Break spacing</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>120 preferred, 60 absolute minimum</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Prevents false break infeasibility on overnight-heavy 24/7 schedules</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60-min absolute minimum</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Blank demand</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>No new staffing in blank intervals</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Avoids invented demand</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>No blank intervals exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Directional source -&gt; cover list</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Prevents over-expanding UK/Bilingual eligibility</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>UK + English; Bilingual + French + English</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E8"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9315,7 +9027,951 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="48" customWidth="1" style="20" min="2" max="2"/>
+    <col width="30" customWidth="1" style="20" min="3" max="3"/>
+    <col width="62" customWidth="1" style="20" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>ADVANCED - engine tuning. Defaults are production-tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="20">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Change these only with a specific reason. They are not per-schedule business settings; the values here are the ones every released result was measured with.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Demand Fit</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Demand Fit Guard Enabled</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr"/>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Demand Fit Minimum Active Minutes</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="D6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Demand Fit Minimum Active Ratio</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr"/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Demand Fit Maximum Blank Span Minutes</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="D8" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Overage Control</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Overage Control Enabled</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr"/>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Overage Soft Cap</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr"/>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Overage Severe Cap</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr"/>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Overage Extreme Cap</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr"/>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Overage Penalty Weight</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Break Concurrency</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Maximum Concurrent Break Ratio</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr"/>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Maximum Concurrent Breaks</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr"/>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Break Concurrency Gate Mode</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Week Boundary</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Next Sunday Balance Enabled</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr"/>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Next Sunday Overage Cap</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr"/>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Next Sunday Maximum Adjacent Raw Change</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr"/>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Next Sunday Balance Gate Mode</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Language / Skill</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Language Operational Reserve Enabled</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr"/>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Language Operational Reserve Extra FTE</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="27" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr"/>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Language Reserve Gate Mode</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Warn</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr"/>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Qualified Language Break Certificate Enabled</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>Whole Week Balance</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Whole Week Balance Enabled</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr"/>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Whole Week Overage Cap</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D31" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Quality Benchmark Tolerance Intervals</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="27" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Auto,Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10 C20 C25 C28 C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C18 C23 C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Warn,Fail,Off"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Input Checks are performed by the engine, not by this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1" s="20">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>The previous version of this tab held hardcoded PASS/WARN text. It reported PASS regardless of what the roster, demand or language setup actually contained, so it could not catch the errors it appeared to check for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>The engine runs the real pre-solver contract validation on every run and writes the result to the audit JSON as pre_solver_contract_validation, with a specific code, day and time for each failure. That is the authoritative check.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" style="20" min="1" max="1"/>
+    <col width="105" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15" customWidth="1" style="20" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>RC9.1 Universal Search-Recovery Production Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="20">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>This workbook is the only input contract for the RC9.1 universal engine. It is prepared for a full 24/7 GDI REAL28 weekly case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Production rule</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Program/client name is metadata only; solver behavior is controlled by Instructions, Shift Library, Language Setup, requests, and requirement sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Primary KPI</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Target is dynamic; this case explicitly targets 100% per interval with 80% protected floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Required output 1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>BEST_BEFORE_BREAKS_SCHEDULE is the review/anchor artifact only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Required output 2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>BEST_FINAL_AFTER_BREAKS_SCHEDULE is the operational after-break artifact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Search Recovery</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>RC9.1 should expand break search across target Pareto skeletons rather than exhaust a single skeleton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Deep Mode</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Default Deep runtime up to 4 hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Full Mode</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Default Full runtime up to 6 hours for tight 24/7 cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Universal Scope</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>No client-specific production branch is implied by Program Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="20">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>24/7 Input Contract</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24x7 operating week; blank demand intervals are intentional and governed by Blank Interval Staffing Rule. Do not force blanks to zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Workbook completion checklist</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Instructions values completed</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="20">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Schedule roster rows completed, one associate per row</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Requirement sheet selected and populated</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="20">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Matching shrinkage sheet selected and populated</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Shift Library contains only allowed 9H shifts</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Language Setup completed</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Request completed/disabled</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Previous week scheduled completed</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Input Checks reviewed before upload</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C23"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="50" customWidth="1" style="20" min="3" max="3"/>
+    <col width="12" customWidth="1" style="20" min="4" max="4"/>
+    <col width="42" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>RC9.1 Release Notes — Input-specific choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>This workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Target handling</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Workbook Target is primary</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Prevents floor-first misoptimization</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Target=100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="20">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2 breaks</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Breadth-first across Pareto skeletons</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Improves recovery on tight 24/7 cases</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Keep default</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Joint recovery</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Deep 4h / Full 6h</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tight 24/7 needs integrated recovery time</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Keep default</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="20">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Break spacing</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>120 preferred, 60 absolute minimum</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Prevents false break infeasibility on overnight-heavy 24/7 schedules</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60-min absolute minimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Blank demand</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No new staffing in blank intervals</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Avoids invented demand</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No blank intervals exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Directional source -&gt; cover list</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Prevents over-expanding UK/Bilingual eligibility</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UK + English; Bilingual + French + English</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9471,1345 +10127,6 @@
   <autoFilter ref="A1:G8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="20" min="1" max="1"/>
-    <col width="40" customWidth="1" style="20" min="2" max="2"/>
-    <col width="34" customWidth="1" style="20" min="3" max="3"/>
-    <col width="65" customWidth="1" style="20" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Instructions — RC9.1 Universal Business Contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>What this controls</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Program Name</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>NMG_EN</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Metadata only; no solver branch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Interval Minutes</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Matches FT Wise 30 Min / Shrinkage 30 Min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Requirements Source</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>FT Wise 30 Min</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Selected demand grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Shrinkage Source</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Shrinkage 30 Min</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Matching shrinkage grid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Primary after-break target tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Target Priority Confirmed</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Confirms this 90% target is intentional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Minimum Per Interval</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Protected floor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Hard Floor Solver Constraint Enabled</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Floor protected; target remains primary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Blank Interval Staffing Rule</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>No new staffing in blank intervals</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>No current-week staffing in blank demand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Allowed Shift Durations Hours</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Only 9H shifts are allowed in this input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Use 11H/3OFF</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Explicitly disabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Strict OFF Count</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2 OFF for 9H/2OFF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="20">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Separate OFF Days</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Normal consecutive OFF preference; explicit preference OFF still honored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Rest Gap Hours</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Minimum rest gap, including week boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Shift &amp; OFF</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Count of Different Shifts Per week</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Maximum distinct shifts in week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Request Use</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Active exact fixed shift/OFF rows in Fixed Request are honored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Hard OFF Preferences</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>OFF in Preference is hard when present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Leave Enabled</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Leave is hard unavailable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Use Preferences</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Soft shift/OFF preferences are used where not hard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Opening Guard</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Opening Guard Enabled</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Not imposed by this input unless business contract is changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Opening Guard</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Opening Minimum FTE</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Control value if enabled later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Opening Guard</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Opening Guard Intervals</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Control value if enabled later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Short Break Count</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Two 15-minute short breaks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Short Break Duration Minutes</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Per short break.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Lunch Count</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>One lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Lunch Duration Minutes</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Lunch duration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Break Preferred Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Preferred spacing, not the hard minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Break Absolute Minimum Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Hard minimum spacing between break segments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Break Normal Maximum Gap Minutes</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Normal spacing target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Breaks</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Allow Back-to-Back Breaks</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>No compressed back-to-back breaks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1" s="20">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Exception Policy</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Critical Coverage No-Break Exception Enabled</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Do not silently allow no-break exceptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1" s="20">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Exception Policy</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Critical Coverage No-Break Max Associate-Days</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>No operational no-break exceptions approved in input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Release Quality</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Production Quality Gate Mode</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Hard-valid schedule can be reviewed if quality debt appears.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Count of Associates</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Must match named roster rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Case Setup</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Allow Headcount Mismatch</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Do not silently accept mismatch.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <dataValidations count="10">
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Enable 11H only when explicitly approved." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Strict OFF count control." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Use fixed/nesting only with real requests." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Hard OFF preference control." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Leave control." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Use soft preferences." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Opening guard." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Back-to-back break override." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="No-break exception permission." type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="RC9.1 input control" prompt="Release gate mode." type="list">
-      <formula1>"Fail,Warn,Off"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" style="20" min="1" max="1"/>
-    <col width="34" customWidth="1" style="20" min="2" max="2"/>
-    <col width="54" customWidth="1" style="20" min="3" max="3"/>
-    <col width="48" customWidth="1" style="20" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" s="20">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Engine Defaults — RC9.1 24/7-safe defaults</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Demand Fit Guard Enabled</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Auto-enable when blank staffing is prohibited.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>24/7 demand has no blank cells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Demand Fit Minimum Active Minutes</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Technical demand-fit guard.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Demand Fit Minimum Active Ratio</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Technical demand-fit guard.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Demand Fit Maximum Blank Span Minutes</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Technical guard default.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No blank span in 24/7 input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Overage Control Enabled</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Discourage avoidable overage after coverage protections.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Overage Soft Cap</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Diagnostic threshold.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Overage Severe Cap</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Diagnostic threshold.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Overage Extreme Cap</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Diagnostic threshold.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Overage Penalty Weight</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Internal objective weight.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Maximum Concurrent Break Ratio</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Operational quality default.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Maximum Concurrent Breaks</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Operational quality default.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Break Concurrency Gate Mode</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Warning unless business changes it.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Next Sunday Balance Enabled</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Protect cyclic carry-out.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Next Sunday Overage Cap</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic balance default.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Next Sunday Maximum Adjacent Raw Change</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Cyclic balance default.</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Next Sunday Balance Gate Mode</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Operational warning by default.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Language Operational Reserve Enabled</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Prefer redundancy over only meeting language minimum.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Language Operational Reserve Extra FTE</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Reserve default.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Language Reserve Gate Mode</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Warn</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Operational warning by default.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Qualified Language Break Certificate Enabled</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Break-feasibility evidence for language coverage.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Whole Week Balance Enabled</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Whole-week balance optimization.</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Whole Week Overage Cap</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Balance default.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Quality Benchmark Tolerance Intervals</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Do not let historical benchmark hide current contract.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>RC9.1 Deep Default Seconds</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>14400</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Approx. 4 hours.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>RC9.1 Full Default Seconds</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>21600</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Approx. 6 hours.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>RC9.1 Stage2 Search Order</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Breadth First</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Expand across Pareto skeletons before exhausting one.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>RC9.1 Joint Budget Policy</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Up to 35% of total runtime</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Allow integrated shift/OFF/break recovery.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D29"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0"/>
